--- a/templates/satisfaction/청소년예방교육만족도.xlsx
+++ b/templates/satisfaction/청소년예방교육만족도.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\night\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\데이터정보화팀\☆0. 통합유지보수\2026년\99. 개별 요청 사항\1월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2DADD4-8CD1-4ABD-B5FB-07447EFE1427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{865F0666-74F0-4CCD-923A-057AECA24A60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="청소년예방교육만족도" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>연령</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -406,15 +406,6 @@
       <t>1</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중학교</t>
-  </si>
-  <si>
-    <t>2학년</t>
-  </si>
-  <si>
-    <t>여</t>
   </si>
 </sst>
 </file>
@@ -938,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.375" style="10" customWidth="1"/>
@@ -1009,50 +1000,6 @@
       </c>
       <c r="N2" s="9" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="10">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="10">
-        <v>4</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
-      <c r="H3" s="10">
-        <v>1</v>
-      </c>
-      <c r="I3" s="10">
-        <v>1</v>
-      </c>
-      <c r="J3" s="10">
-        <v>1</v>
-      </c>
-      <c r="K3" s="10">
-        <v>4</v>
-      </c>
-      <c r="L3" s="10">
-        <v>4</v>
-      </c>
-      <c r="M3" s="10">
-        <v>4</v>
-      </c>
-      <c r="N3" s="10">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
